--- a/龙虎榜_股票汇总.xlsx
+++ b/龙虎榜_股票汇总.xlsx
@@ -577,7 +577,7 @@
         <v>1.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="7">
@@ -601,7 +601,7 @@
         <v>4.89</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5700000000000003</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
         <v>4230.84</v>
       </c>
       <c r="F13" t="n">
-        <v>-4225.190000000001</v>
+        <v>-4225.19</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +841,7 @@
         <v>-1.21</v>
       </c>
       <c r="F17" t="n">
-        <v>9.489999999999998</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="18">
@@ -1033,7 +1033,7 @@
         <v>3729.44</v>
       </c>
       <c r="F25" t="n">
-        <v>463.7000000000003</v>
+        <v>463.7</v>
       </c>
     </row>
     <row r="26">
@@ -1081,7 +1081,7 @@
         <v>-1509.64</v>
       </c>
       <c r="F27" t="n">
-        <v>7040.070000000001</v>
+        <v>7040.07</v>
       </c>
     </row>
     <row r="28">
@@ -1105,7 +1105,7 @@
         <v>-187.33</v>
       </c>
       <c r="F28" t="n">
-        <v>628.5500000000001</v>
+        <v>628.55</v>
       </c>
     </row>
     <row r="29">
@@ -1753,7 +1753,7 @@
         <v>1.72</v>
       </c>
       <c r="F55" t="n">
-        <v>9.309999999999999</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="56">
@@ -1777,7 +1777,7 @@
         <v>5954.68</v>
       </c>
       <c r="F56" t="n">
-        <v>-5953.110000000001</v>
+        <v>-5953.11</v>
       </c>
     </row>
     <row r="57">
@@ -1801,7 +1801,7 @@
         <v>1.08</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="58">
@@ -1825,7 +1825,7 @@
         <v>-7162.48</v>
       </c>
       <c r="F58" t="n">
-        <v>7164.969999999999</v>
+        <v>7164.97</v>
       </c>
     </row>
     <row r="59">
@@ -1873,7 +1873,7 @@
         <v>4449.35</v>
       </c>
       <c r="F60" t="n">
-        <v>-216.2000000000007</v>
+        <v>-216.2</v>
       </c>
     </row>
     <row r="61">
@@ -1945,7 +1945,7 @@
         <v>-8316.940000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>8319.890000000001</v>
+        <v>8319.889999999999</v>
       </c>
     </row>
     <row r="64">
@@ -1969,7 +1969,7 @@
         <v>-824.02</v>
       </c>
       <c r="F64" t="n">
-        <v>6800.780000000001</v>
+        <v>6800.78</v>
       </c>
     </row>
     <row r="65">
@@ -2041,7 +2041,7 @@
         <v>414.41</v>
       </c>
       <c r="F67" t="n">
-        <v>8200.210000000001</v>
+        <v>8200.209999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2185,7 +2185,7 @@
         <v>-1.23</v>
       </c>
       <c r="F73" t="n">
-        <v>5.869999999999999</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="74">
@@ -2305,7 +2305,7 @@
         <v>1.61</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="79">
